--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -675,38 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129334133</v>
+        <v>129334066</v>
       </c>
       <c r="B2" t="n">
-        <v>97755</v>
+        <v>57724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220686</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>311135</v>
+        <v>311203</v>
       </c>
       <c r="R2" t="n">
-        <v>6410542</v>
+        <v>6410584</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spår av födosök.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,7 +777,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,42 +795,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129334066</v>
+        <v>129334133</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>97755</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>311203</v>
+        <v>311135</v>
       </c>
       <c r="R3" t="n">
-        <v>6410584</v>
+        <v>6410542</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,12 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår av födosök.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,6 +888,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>129334133</v>
       </c>
       <c r="B3" t="n">
-        <v>97755</v>
+        <v>97781</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>129334133</v>
       </c>
       <c r="B3" t="n">
-        <v>97781</v>
+        <v>97782</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -675,42 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129334066</v>
+        <v>129334133</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>97783</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220686</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>311203</v>
+        <v>311135</v>
       </c>
       <c r="R2" t="n">
-        <v>6410584</v>
+        <v>6410542</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spår av födosök.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,6 +768,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,38 +787,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129334133</v>
+        <v>129334066</v>
       </c>
       <c r="B3" t="n">
-        <v>97782</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220686</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>311135</v>
+        <v>311203</v>
       </c>
       <c r="R3" t="n">
-        <v>6410542</v>
+        <v>6410584</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +875,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spår av födosök.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,7 +889,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129334133</v>
       </c>
       <c r="B2" t="n">
-        <v>97783</v>
+        <v>97787</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,38 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129334133</v>
+        <v>129334066</v>
       </c>
       <c r="B2" t="n">
-        <v>97787</v>
+        <v>57724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220686</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>311135</v>
+        <v>311203</v>
       </c>
       <c r="R2" t="n">
-        <v>6410542</v>
+        <v>6410584</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spår av födosök.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,7 +777,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,42 +795,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129334066</v>
+        <v>129334133</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>97787</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>311203</v>
+        <v>311135</v>
       </c>
       <c r="R3" t="n">
-        <v>6410584</v>
+        <v>6410542</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,12 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår av födosök.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,6 +888,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -904,6 +904,126 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129468995</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97787</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Korseberget, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>311173</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6410573</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Harestad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Inka Eriksson, Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -675,42 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129334066</v>
+        <v>129334133</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>97789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220686</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>311203</v>
+        <v>311135</v>
       </c>
       <c r="R2" t="n">
-        <v>6410584</v>
+        <v>6410542</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spår av födosök.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,6 +768,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,38 +787,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129334133</v>
+        <v>129334066</v>
       </c>
       <c r="B3" t="n">
-        <v>97787</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220686</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>311135</v>
+        <v>311203</v>
       </c>
       <c r="R3" t="n">
-        <v>6410542</v>
+        <v>6410584</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +875,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spår av födosök.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,7 +889,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -910,7 +910,7 @@
         <v>129468995</v>
       </c>
       <c r="B4" t="n">
-        <v>97787</v>
+        <v>97789</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129334133</v>
       </c>
       <c r="B2" t="n">
-        <v>97789</v>
+        <v>97793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129468995</v>
       </c>
       <c r="B4" t="n">
-        <v>97789</v>
+        <v>97793</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -675,38 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129334133</v>
+        <v>129334066</v>
       </c>
       <c r="B2" t="n">
-        <v>97793</v>
+        <v>57724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220686</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>311135</v>
+        <v>311203</v>
       </c>
       <c r="R2" t="n">
-        <v>6410542</v>
+        <v>6410584</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spår av födosök.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,7 +777,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,42 +795,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129334066</v>
+        <v>129334133</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>97801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>311203</v>
+        <v>311135</v>
       </c>
       <c r="R3" t="n">
-        <v>6410584</v>
+        <v>6410542</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,12 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår av födosök.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,6 +888,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -910,7 +910,7 @@
         <v>129468995</v>
       </c>
       <c r="B4" t="n">
-        <v>97793</v>
+        <v>97801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>129334133</v>
       </c>
       <c r="B3" t="n">
-        <v>97801</v>
+        <v>97804</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129468995</v>
       </c>
       <c r="B4" t="n">
-        <v>97801</v>
+        <v>97804</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -675,42 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129334066</v>
+        <v>129334133</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>97804</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220686</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>311203</v>
+        <v>311135</v>
       </c>
       <c r="R2" t="n">
-        <v>6410584</v>
+        <v>6410542</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spår av födosök.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,6 +768,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,38 +787,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129334133</v>
+        <v>129334066</v>
       </c>
       <c r="B3" t="n">
-        <v>97804</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220686</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>311135</v>
+        <v>311203</v>
       </c>
       <c r="R3" t="n">
-        <v>6410542</v>
+        <v>6410584</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +875,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spår av födosök.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,7 +889,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -675,38 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129334133</v>
+        <v>129334066</v>
       </c>
       <c r="B2" t="n">
-        <v>97804</v>
+        <v>57724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220686</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>311135</v>
+        <v>311203</v>
       </c>
       <c r="R2" t="n">
-        <v>6410542</v>
+        <v>6410584</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spår av födosök.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,7 +777,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,42 +795,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129334066</v>
+        <v>129334133</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>97804</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>311203</v>
+        <v>311135</v>
       </c>
       <c r="R3" t="n">
-        <v>6410584</v>
+        <v>6410542</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,12 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår av födosök.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,6 +888,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -675,42 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129334066</v>
+        <v>129334133</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>97833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220686</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>311203</v>
+        <v>311135</v>
       </c>
       <c r="R2" t="n">
-        <v>6410584</v>
+        <v>6410542</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spår av födosök.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,6 +768,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,38 +787,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129334133</v>
+        <v>129334066</v>
       </c>
       <c r="B3" t="n">
-        <v>97804</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220686</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>311135</v>
+        <v>311203</v>
       </c>
       <c r="R3" t="n">
-        <v>6410542</v>
+        <v>6410584</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +875,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spår av födosök.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,7 +889,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -910,7 +910,7 @@
         <v>129468995</v>
       </c>
       <c r="B4" t="n">
-        <v>97804</v>
+        <v>97833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -675,38 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129334133</v>
+        <v>129334066</v>
       </c>
       <c r="B2" t="n">
-        <v>97833</v>
+        <v>57732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220686</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>311135</v>
+        <v>311203</v>
       </c>
       <c r="R2" t="n">
-        <v>6410542</v>
+        <v>6410584</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spår av födosök.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,7 +777,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,42 +795,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129334066</v>
+        <v>129334133</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>97845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>311203</v>
+        <v>311135</v>
       </c>
       <c r="R3" t="n">
-        <v>6410584</v>
+        <v>6410542</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,12 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår av födosök.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,6 +888,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -910,7 +910,7 @@
         <v>129468995</v>
       </c>
       <c r="B4" t="n">
-        <v>97833</v>
+        <v>97845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129334066</v>
       </c>
       <c r="B2" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129334133</v>
       </c>
       <c r="B3" t="n">
-        <v>97845</v>
+        <v>97846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129468995</v>
       </c>
       <c r="B4" t="n">
-        <v>97845</v>
+        <v>97846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Inka Eriksson, Mats Eriksson</t>
+          <t>Mats Eriksson, Inka Eriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>129334133</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>97851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129468995</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>97851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mats Eriksson, Inka Eriksson</t>
+          <t>Inka Eriksson, Mats Eriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -675,42 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129334066</v>
+        <v>129334133</v>
       </c>
       <c r="B2" t="n">
-        <v>57733</v>
+        <v>97851</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220686</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>311203</v>
+        <v>311135</v>
       </c>
       <c r="R2" t="n">
-        <v>6410584</v>
+        <v>6410542</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spår av födosök.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,6 +768,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,38 +787,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129334133</v>
+        <v>129334066</v>
       </c>
       <c r="B3" t="n">
-        <v>97851</v>
+        <v>57733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220686</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>311135</v>
+        <v>311203</v>
       </c>
       <c r="R3" t="n">
-        <v>6410542</v>
+        <v>6410584</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +875,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spår av födosök.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,7 +889,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>129468995</v>
       </c>
       <c r="B4" t="n">
-        <v>97851</v>
+        <v>97855</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>129468995</v>
       </c>
       <c r="B4" t="n">
-        <v>97855</v>
+        <v>97857</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -1030,7 +1030,7 @@
         <v>130990069</v>
       </c>
       <c r="B5" t="n">
-        <v>96605</v>
+        <v>96608</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -1030,7 +1030,7 @@
         <v>130990069</v>
       </c>
       <c r="B5" t="n">
-        <v>96608</v>
+        <v>96609</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -1351,7 +1351,7 @@
         <v>131073777</v>
       </c>
       <c r="B8" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>131153866</v>
       </c>
       <c r="B9" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>131204141</v>
       </c>
       <c r="B10" t="n">
-        <v>58322</v>
+        <v>58324</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>131223036</v>
       </c>
       <c r="B11" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -1351,7 +1351,7 @@
         <v>131073777</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>131153866</v>
       </c>
       <c r="B9" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>131204141</v>
       </c>
       <c r="B10" t="n">
-        <v>58324</v>
+        <v>58325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>131223036</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -1351,7 +1351,7 @@
         <v>131073777</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>131153866</v>
       </c>
       <c r="B9" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>131204141</v>
       </c>
       <c r="B10" t="n">
-        <v>58325</v>
+        <v>58326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>131223036</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -1453,7 +1453,7 @@
         <v>131153866</v>
       </c>
       <c r="B9" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>131204141</v>
       </c>
       <c r="B10" t="n">
-        <v>58326</v>
+        <v>58329</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>131223036</v>
       </c>
       <c r="B11" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -1453,7 +1453,7 @@
         <v>131153866</v>
       </c>
       <c r="B9" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>131204141</v>
       </c>
       <c r="B10" t="n">
-        <v>58329</v>
+        <v>58330</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>131223036</v>
       </c>
       <c r="B11" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -1453,7 +1453,7 @@
         <v>131153866</v>
       </c>
       <c r="B9" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>131204141</v>
       </c>
       <c r="B10" t="n">
-        <v>58330</v>
+        <v>58336</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>131223036</v>
       </c>
       <c r="B11" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -1677,7 +1677,7 @@
         <v>131223036</v>
       </c>
       <c r="B11" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129334133</v>
+        <v>130990069</v>
       </c>
       <c r="B2" t="n">
-        <v>97851</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,38 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220686</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Korseberget, Boh</t>
+          <t>Skansen, Skansen, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>311135</v>
+        <v>311315</v>
       </c>
       <c r="R2" t="n">
-        <v>6410542</v>
+        <v>6410544</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -744,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,19 +754,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -790,11 +775,11 @@
         <v>129334066</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -907,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129468995</v>
+        <v>130991521</v>
       </c>
       <c r="B4" t="n">
-        <v>97857</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,49 +903,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220686</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Korseberget, Boh</t>
+          <t>Skansen, Skansen, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>311173</v>
+        <v>311227</v>
       </c>
       <c r="R4" t="n">
-        <v>6410573</v>
+        <v>6410581</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,22 +957,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,29 +986,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Inka Eriksson, Mats Eriksson</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130990069</v>
+        <v>130992753</v>
       </c>
       <c r="B5" t="n">
-        <v>96609</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,34 +1015,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skansen, Skansen, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>311315</v>
+        <v>311161</v>
       </c>
       <c r="R5" t="n">
-        <v>6410544</v>
+        <v>6410641</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,9 +1077,19 @@
           <t>2026-02-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,14 +1116,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130991521</v>
+        <v>131073777</v>
       </c>
       <c r="B6" t="n">
-        <v>57881</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1153,19 +1145,24 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skansen, Skansen, Boh</t>
+          <t>Stötetorpet, Stötetorpet, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>311227</v>
+        <v>311113</v>
       </c>
       <c r="R6" t="n">
-        <v>6410581</v>
+        <v>6410575</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,27 +1186,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,26 +1206,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130993250</v>
+        <v>131223036</v>
       </c>
       <c r="B7" t="n">
-        <v>57881</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1264,22 +1246,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stötetorpet, Stötetorpet, Boh</t>
+          <t>Korseberget, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>311161</v>
+        <v>311091</v>
       </c>
       <c r="R7" t="n">
-        <v>6410641</v>
+        <v>6410588</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,22 +1299,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Inspelad i fält på platsen med en Audiomoth  inspelningsapparat</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131073777</v>
+        <v>131204141</v>
       </c>
       <c r="B8" t="n">
-        <v>57885</v>
+        <v>58393</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,39 +1357,50 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>102999</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stötetorpet, Stötetorpet, Boh</t>
+          <t>Korseberget, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>311113</v>
+        <v>311219</v>
       </c>
       <c r="R8" t="n">
-        <v>6410575</v>
+        <v>6410570</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,12 +1427,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Inspelad i fält med Audiomoth ljudbox.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,7 +1467,7 @@
         <v>131153866</v>
       </c>
       <c r="B9" t="n">
-        <v>58057</v>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,61 +1570,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131204141</v>
+        <v>129334133</v>
       </c>
       <c r="B10" t="n">
-        <v>58336</v>
+        <v>98194</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102999</v>
+        <v>220686</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Korseberget, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>311219</v>
+        <v>311135</v>
       </c>
       <c r="R10" t="n">
-        <v>6410570</v>
+        <v>6410542</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,17 +1639,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Inspelad i fält med Audiomoth ljudbox.</t>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,79 +1663,76 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131223036</v>
+        <v>129468995</v>
       </c>
       <c r="B11" t="n">
-        <v>57896</v>
+        <v>98194</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220686</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Korseberget, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>311091</v>
+        <v>311173</v>
       </c>
       <c r="R11" t="n">
-        <v>6410588</v>
+        <v>6410573</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1755,27 +1759,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Inspelad i fält på platsen med en Audiomoth  inspelningsapparat</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1784,18 +1783,19 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson, Mats Eriksson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 6041-2025 artfynd.xlsx
+++ b/artfynd/A 6041-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130990069</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129334066</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130991521</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130992753</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131073777</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131223036</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1461,6 +1496,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131204141</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1567,6 +1607,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153866</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1679,6 +1724,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129334133</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1799,8 +1849,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129468995</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>